--- a/samples/표준_현황엑셀_빈양식.xlsx
+++ b/samples/표준_현황엑셀_빈양식.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Z1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,43 +417,79 @@
         <v>운전자</v>
       </c>
       <c r="F1" t="str">
+        <v>주/야/휴</v>
+      </c>
+      <c r="G1" t="str">
+        <v>날씨</v>
+      </c>
+      <c r="H1" t="str">
         <v>시작 아워미터(h)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>종료 아워미터(h)</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>운행시간(h)</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
+        <v>충전시간(h)</v>
+      </c>
+      <c r="L1" t="str">
+        <v>기본/요철 사이클(h)</v>
+      </c>
+      <c r="M1" t="str">
+        <v>기본 사이클(회)</v>
+      </c>
+      <c r="N1" t="str">
+        <v>요철 사이클(회)</v>
+      </c>
+      <c r="O1" t="str">
+        <v>배터리 충전 점검(h)</v>
+      </c>
+      <c r="P1" t="str">
+        <v>장비 점검·TPR 작성(h)</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>특화 장비수리(h)</v>
+      </c>
+      <c r="R1" t="str">
+        <v>히터 가동(h)</v>
+      </c>
+      <c r="S1" t="str">
+        <v>에어컨 가동(h)</v>
+      </c>
+      <c r="T1" t="str">
         <v>배터리소모율(%)</v>
       </c>
-      <c r="J1" t="str">
+      <c r="U1" t="str">
         <v>충전량(kWh)</v>
       </c>
-      <c r="K1" t="str">
+      <c r="V1" t="str">
         <v>연료 종류</v>
       </c>
-      <c r="L1" t="str">
+      <c r="W1" t="str">
         <v>연료 소모량</v>
       </c>
-      <c r="M1" t="str">
+      <c r="X1" t="str">
+        <v>요소수 주입량(L)</v>
+      </c>
+      <c r="Y1" t="str">
         <v>문제점</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Z1" t="str">
         <v>사진 참조</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -533,116 +569,248 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>시작 아워미터(h)</v>
+        <v>주/야/휴</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>일지 시작 때 아워미터 누적값</v>
+        <v>주 / 야 / 휴 (주간·야간·휴일도 됩니다)</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>종료 아워미터(h)</v>
+        <v>날씨</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>일지 끝날 때 아워미터 누적값</v>
+        <v>맑음·흐림·비 등</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>운행시간(h)</v>
+        <v>시작 아워미터(h)</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>비우면 종료−시작으로 계산. 3:30 처럼 시:분도 됩니다</v>
+        <v>일지 시작 때 아워미터 누적값</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>배터리소모율(%)</v>
+        <v>종료 아워미터(h)</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>전동 모델, 0~100</v>
+        <v>일지 끝날 때 아워미터 누적값</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>충전량(kWh)</v>
+        <v>운행시간(h)</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>전동 모델 충전량</v>
+        <v>비우면 종료−시작으로 계산. 3:30 처럼 시:분도 됩니다</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>연료 종류</v>
+        <v>충전시간(h)</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>경유 / LPG / 전기</v>
+        <v>TPR 「금일충전시간」</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>연료 소모량</v>
+        <v>기본/요철 사이클(h)</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>경유·LPG 소모량(단위는 기성 화면에서 지정)</v>
+        <v>TPR 「기본/요철 사이클」 시간</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>문제점</v>
+        <v>기본 사이클(회)</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>문제점 문장 그대로</v>
+        <v>기본 사이클 회수</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>사진 참조</v>
+        <v>요철 사이클(회)</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>사진 파일명이나 보관 위치</v>
+        <v>요철 사이클 회수</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>배터리 충전 점검(h)</v>
+      </c>
+      <c r="B18" t="str">
+        <v/>
+      </c>
+      <c r="C18" t="str">
+        <v>TPR 「배터리 충전 점검」 시간</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>장비 점검·TPR 작성(h)</v>
+      </c>
+      <c r="B19" t="str">
+        <v/>
+      </c>
+      <c r="C19" t="str">
+        <v>TPR 「장비 점검/TPR 작성」 시간</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>특화 장비수리(h)</v>
+      </c>
+      <c r="B20" t="str">
+        <v/>
+      </c>
+      <c r="C20" t="str">
+        <v>정리 엑셀 「특회 장비 수리」 시간</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>히터 가동(h)</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>히터 가동 시간</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>에어컨 가동(h)</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>에어컨 가동 시간</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>배터리소모율(%)</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>전동 모델, 0~100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>충전량(kWh)</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>전동 모델 충전량</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>연료 종류</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>경유 / LPG / 전기</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>연료 소모량</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>경유 L · LPG kg 주입량(주입한 날만)</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>요소수 주입량(L)</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>요소수 주입량(L)</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>문제점</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>문제점 문장 그대로</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>사진 참조</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v>사진 파일명이나 보관 위치</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
         <v>한 행 = 일지 한 장입니다. 열 이름은 샘플 확인 후 바뀔 수 있습니다(가정).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/표준_현황엑셀_빈양식.xlsx
+++ b/samples/표준_현황엑셀_빈양식.xlsx
@@ -450,7 +450,7 @@
         <v>장비 점검·TPR 작성(h)</v>
       </c>
       <c r="Q1" t="str">
-        <v>특화 장비수리(h)</v>
+        <v>특화 시험·장비수리(h)</v>
       </c>
       <c r="R1" t="str">
         <v>히터 가동(h)</v>
@@ -690,13 +690,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>특화 장비수리(h)</v>
+        <v>특화 시험·장비수리(h)</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>정리 엑셀 「특회 장비 수리」 시간</v>
+        <v>특화 시험(동력전달 특화 등)·장비수리 시간 — 정리 엑셀 「특회 장비 수리」 칸</v>
       </c>
     </row>
     <row r="21">

--- a/samples/표준_현황엑셀_빈양식.xlsx
+++ b/samples/표준_현황엑셀_빈양식.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AB1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -474,22 +474,28 @@
         <v>요소수 주입량(L)</v>
       </c>
       <c r="Y1" t="str">
+        <v>경유 결제 금액(원)</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>요소수 결제 금액(원)</v>
+      </c>
+      <c r="AA1" t="str">
         <v>문제점</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>사진 참조</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -778,39 +784,61 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>문제점</v>
+        <v>경유 결제 금액(원)</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>문제점 문장 그대로</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>사진 참조</v>
+        <v>요소수 결제 금액(원)</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>사진 파일명이나 보관 위치</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
+        <v>문제점</v>
+      </c>
+      <c r="B30" t="str">
+        <v/>
+      </c>
+      <c r="C30" t="str">
+        <v>문제점 문장 그대로</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>사진 참조</v>
+      </c>
+      <c r="B31" t="str">
+        <v/>
+      </c>
+      <c r="C31" t="str">
+        <v>사진 파일명이나 보관 위치</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
         <v>한 행 = 일지 한 장입니다. 열 이름은 샘플 확인 후 바뀔 수 있습니다(가정).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C33"/>
   </ignoredErrors>
 </worksheet>
 </file>